--- a/AAII_Financials/Quarterly/TX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TX_QTR_FIN.xlsx
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4340300</v>
+      </c>
+      <c r="E8" s="3">
         <v>3934000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3774800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3954600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3946900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3932800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3876300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4480400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4514200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4778300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4930700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5184700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3871300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3623400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3546500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4125500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4437700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4304800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4329700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4592000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3919800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3249300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2579700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2138600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1745800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2271400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2250000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2449700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2757300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2735800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2636100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2999200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3022400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2797000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2918000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2479500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2262600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2075100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1849600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1856100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3399300</v>
+      </c>
+      <c r="E9" s="3">
         <v>3250600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3173900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3346200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3336900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3404400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3429400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3901900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3757600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3677600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4041400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4192000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2839400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2982600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3119000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3325200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3058900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2984200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2720000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2621100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2415700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2138300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1914100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1756600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1508800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1920500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1943300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4010500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2277700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4431600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2059900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4090900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2212400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2132700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2265900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1572400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1668200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1531500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1416600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1291300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>941000</v>
+      </c>
+      <c r="E10" s="3">
         <v>683300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>600900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>608400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>610100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>528500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>446800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>578400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>756600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1100700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>889400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>992700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1031900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>640800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>427500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>800300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1378800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1320600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1609700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1970900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1504100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1111000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>665600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>382000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>237000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>350900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>306700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-1560800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>479600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-1695800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>576200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-1091700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>810000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>664300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>652100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>907100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>594400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>543600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>433000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>564800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,19 +1248,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>21800</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1255,11 +1269,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>23800</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1267,11 +1281,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>19000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,43 +1496,46 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E14" s="3">
         <v>30800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-16300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>31600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>39700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>12300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-460300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>31000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>783000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>133800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-90400</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1532,8 +1552,8 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1565,14 +1585,14 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1580,17 +1600,17 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>55500</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>344500</v>
-      </c>
-      <c r="AM14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AN14" s="3" t="s">
         <v>8</v>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>193700</v>
+      </c>
+      <c r="E15" s="3">
         <v>180700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>42700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>197100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>196800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>184100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>51800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>184300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>199300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>170900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>61200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>165200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>150900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>10400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>10500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>10100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>9400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>10000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>9700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>15300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>18500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>15600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>17900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>24800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>30900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>35100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>27300</v>
       </c>
-      <c r="AE15" s="3" t="s">
+      <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>33300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>10900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>26800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>32300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>37800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>47500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>18800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>12100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>12300</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>12600</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3811900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3643900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3616300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3739200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3747700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3801000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3894300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4304900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4143600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4103400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4517500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4657400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3139500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3266000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3503400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3599200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3366500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3245800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2971100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2856600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2648300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2343500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1902500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2131700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1680200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2135700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2157800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2221100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2520900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2428500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2253400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2290300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2451900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2350800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2568100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2129700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1869800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1711000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1602900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1456900</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>528400</v>
+      </c>
+      <c r="E18" s="3">
         <v>290100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>158500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>215400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>199200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>131800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-18000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>175500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>370500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>674900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>413200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>527300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>731700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>357400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>43100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>526300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1071200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1059000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1358600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1735400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1271500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>905800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>677200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>65600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>135700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>92200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>228600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>236400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>307300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>382700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>708900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>570500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>446200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>349900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>349800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>392800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>364100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>246700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>399200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>25600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>12600</v>
       </c>
-      <c r="G20" s="3">
-        <v>4600</v>
-      </c>
       <c r="H20" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-31400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>63800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-73800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>23800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>46900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-156300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1087500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>15200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>45400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-130000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>93700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>126100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>123600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>69700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>10200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>8500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-20800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>128500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>37400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>17900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>95200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>7700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>138200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-30600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-57700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>26700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>16000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-27800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>2900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>29500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>710400</v>
+      </c>
+      <c r="E21" s="3">
         <v>477400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>175700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>399900</v>
       </c>
-      <c r="G21" s="3">
-        <v>391300</v>
-      </c>
       <c r="H21" s="3">
+        <v>390200</v>
+      </c>
+      <c r="I21" s="3">
         <v>347400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-30000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>433600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>546000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>798800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>630800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-395000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>867500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>386000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>249000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>549400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1318300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1213000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1630900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2004200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1621000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1127100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>841400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>167800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>203200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>430600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>300500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>405900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>499600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>477900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>651000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>825900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>667100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>604600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>529000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>482100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>470000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>467600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>380100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>518800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E22" s="3">
         <v>50200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>50400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>53300</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3">
+        <v>56300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>54300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>52100</v>
+      </c>
+      <c r="K22" s="3">
+        <v>54100</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="3">
-        <v>54300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>52100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>54100</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>44900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>44300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>47300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>17500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>14600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>43500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>51000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>81900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>19800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>29600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>36700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>31300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>30100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>39900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>29200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>24100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>21400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>26700</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>27900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>487400</v>
+      </c>
+      <c r="E23" s="3">
         <v>279400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>154600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>173700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>154900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>165100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>396900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>235500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-436300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>531900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>709500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-529800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>741100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>400100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>70400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>381600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1157600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1056900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1478200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1852500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1465400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>968300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>679700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>31300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>247900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>86100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>195600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>249700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>295200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>491300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>641600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>481400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>417300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>336700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>336600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>340900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>345600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>249600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>387700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-93000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-16700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>443600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-104400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>142800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>306800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>40400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>155600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>253000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-79400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>161700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>221400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>179400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>342400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>486000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>307100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>261600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>27500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>267300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>83600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>46500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>70300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>55800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>80800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>192200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>40600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>143900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>103800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>59100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>35200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>104800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>464500</v>
+      </c>
+      <c r="E26" s="3">
         <v>372400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>171300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-269900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>259300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>142300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>332800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>92700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-743100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>491400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>553800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-782800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>735900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>479500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>59200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>219900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>936200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>877500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1135800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1366400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1158300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>706700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>670600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-21100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>43600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>89900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>111900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>203200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>224900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>435400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>560800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>289300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>376700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>192800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>232700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>281800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>310400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>144800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>264300</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>343700</v>
+      </c>
+      <c r="E27" s="3">
         <v>213000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>122200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>215400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>67000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>280900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>31700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-727600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>361400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>413900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-739100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>626900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>374400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>39800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>152800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>799300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>775600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>998000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1202100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1022100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>602900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>600400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-48500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>44000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>70500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>95300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>180200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>218200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>350600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>523600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>293700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>338900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>175000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>194900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>249700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>261300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>118400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>228900</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3236,8 +3297,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>5200</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E32" s="3">
         <v>6600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-25600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-12600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-4600</v>
-      </c>
       <c r="H32" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="I32" s="3">
         <v>31400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-63800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>73800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-23800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-46900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>156300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1087500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-15200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>17500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-45400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>130000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-93700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-126100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-123600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-69700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>20800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-128500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-37400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-95200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-138200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>30600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>57700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-26700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>27800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-29500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>343700</v>
+      </c>
+      <c r="E33" s="3">
         <v>213000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>122200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>215400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>67000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>280900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>31700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-727600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>361400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>413900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-739100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>626900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>374400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>39800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>152800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>799300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>775600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>998000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1202100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1022100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>602900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>600400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-48500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>44000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>70500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>95300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>180200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>218200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>350600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>523600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>293700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>338900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>180200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>194900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>249700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>261300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>118400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>228900</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>343700</v>
+      </c>
+      <c r="E35" s="3">
         <v>213000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>122200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>215400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>67000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>280900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>31700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-727600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>361400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>413900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-739100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>626900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>374400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>39800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>152800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>799300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>775600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>998000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1202100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1022100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>602900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>600400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-48500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>44000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>70500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>95300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>180200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>218200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>350600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>523600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>293700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>338900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>180200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>194900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>249700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>261300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>118400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>228900</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,1106 +4305,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1430700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1617300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1531200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1322900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1857700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1831200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1691300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1614300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1719500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1780500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1846000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1815700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>920400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1220100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1653400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1474200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>719100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1790300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1276600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>947600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>768700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>835400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>537900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>680700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>454600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>906400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>520000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>637700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>777500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>464300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>250500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>399100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>229800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>232600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>337800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>383800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>178300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>286000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>183500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>149400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1300700</v>
+      </c>
+      <c r="E42" s="3">
         <v>1524900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1600000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1437600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1517200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1924200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2160100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2243200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2117100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2282800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1975600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2468800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2031800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2521700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1875000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1268400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1340100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1134700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1290500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>768500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>616000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>637500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>813500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>623200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>704100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>115200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>212300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>214000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>28600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>61800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>44500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>61000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>97900</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>103900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>132700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>157200</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>153200</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>151500</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>144900</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>189900</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2714000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2587900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2449400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2838800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2636500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2693900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2378800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2836000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2941700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3402200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3155100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3334100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2131700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2060000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1843500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2061700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2440000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2326800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2124900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2394300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2070400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1714300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1207000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>993300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>900600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1211000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1284400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1369800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1680400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1560600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1438200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1523300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1536500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1659400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1368800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1384300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1044300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>933500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>713600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>782800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4395100</v>
+      </c>
+      <c r="E44" s="3">
         <v>4172500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4093700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4132400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4228200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4591300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4750500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5019100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5048000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5059500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4948400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5135900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3758600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3297600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3470200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3966300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4540400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3780500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3908300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3626400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2945200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2345000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2001800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1667300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1803900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2083600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2158300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2336300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2447600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2566400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2689800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2670500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2589400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2688600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2550900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2357200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1963600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1897400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1647900</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1570500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E45" s="3">
         <v>33500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>122100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>83700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>109200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>97500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>105400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6600</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1800</v>
       </c>
       <c r="P45" s="3">
         <v>1800</v>
       </c>
       <c r="Q45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>17300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>6300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>39500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>13200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9875800</v>
+      </c>
+      <c r="E46" s="3">
         <v>9936200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9796400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9815300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10348700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11056000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11078100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11744900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11841500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12541000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12030500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12761100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8844200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9101300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8842300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8777000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9047100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9032800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8604600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>7738200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6403600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5533700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4561800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3965900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3870900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4333500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4176100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4562500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4934200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4654300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4423900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4657300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4455300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4687200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4392500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4288800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3378900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3281500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2690100</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2694500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>614100</v>
+      </c>
+      <c r="E47" s="3">
         <v>590300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>562900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>582400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>553800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>509800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>491500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>544200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>528500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>559200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>728200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>775500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1041900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1002400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1241000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1126300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1196000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1192400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>996800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>917600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>911200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>681300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>717500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>664300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>880200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>919400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1110400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1070200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1163600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1139700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1156600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1116100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1111000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1234700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1163900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>853700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>603400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>606400</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>558200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>534500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10973000</v>
+      </c>
+      <c r="E48" s="3">
         <v>10708900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10406100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10104300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9486200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8803100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8381200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8141900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7911200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7855900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7637700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7384000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6324300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6294200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6261900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6381500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6407600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6406400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6431600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6462500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6494300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6488500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6504700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6525800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6596700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6636300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6539600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6295800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6375100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6166100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5817600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5594900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5138800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5298200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5349800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>5023700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4160200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>4222000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>4136000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>4158700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1037400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1007500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1002400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1017800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1024600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1018900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1022100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1062100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1049700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1024900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>996000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1029000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>968100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>957400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>944400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>927100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>915600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>903900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>902300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>897000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>895900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>893200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>908600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>908300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>915700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>927800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>943800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>945000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>968600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>990900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1012500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1006100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1027400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1058200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1092600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1132500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>831900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>834600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>842600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>847400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>764100</v>
+      </c>
+      <c r="E52" s="3">
         <v>777900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>803900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>904100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1077000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1029500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>961300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1013000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>943500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>994200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1073200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>808700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>409400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>327600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>202000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>210100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>224200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>185000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>162700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>159300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>145500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>156600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>163700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>128700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>126200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>121800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>165600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>130500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>141700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>150000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>137200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>121500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>131300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>137200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>123900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>127400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>121200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>117200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>96000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>97700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24551800</v>
+      </c>
+      <c r="E54" s="3">
         <v>24242200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23615100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23471400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23919200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23715600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23128500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23938500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23663100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24669300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24179100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24285000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17936800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17906500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17491500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17421900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17790500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17720500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17097900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16174600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14850600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13753200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12856200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12193000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12389600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12938800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12935500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13004100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13583300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13100900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12547900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12495900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11863800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12415600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12122600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11426200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>9095600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9061700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>8322900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>8332700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2035700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2078500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2074000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2128200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2022200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1835800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1926000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1992000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2250100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2194900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2236200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2199400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1321900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1356800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1187600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1121300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1564500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1422200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1126000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1222300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1404100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1179100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1049300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>824600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>738500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>994100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>876800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>918400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1014300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1045700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>904200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>957800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1027300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1061000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>897700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>992000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>768100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>707300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>603100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>588300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>684900</v>
+      </c>
+      <c r="E58" s="3">
         <v>665000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>652900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>602500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>596400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>688100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>716500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>640200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>802200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>969200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>992600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1023000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>423900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>399900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>548200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>590900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>597300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>754000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>866900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>772700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>643500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>619400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>438100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>450000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>627900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>735200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>600300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>661800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>778500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>607200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>407900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>866400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1281200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1317200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1505600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1414900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1246600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>998300</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>821900</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>914500</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1102800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1029200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>951600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1259300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1238300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1159000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>914100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1390200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1272200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>611800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>258500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>705300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>472800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>520600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>481100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>374100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>422600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>645300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1220800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1101700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>797900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>542600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>366200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>251800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>254400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>271300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>291000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>333400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>352200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>481000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>514500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>494100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>469000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>469800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>424000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>419900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>330000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>550400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>406500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>352600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3823400</v>
+      </c>
+      <c r="E60" s="3">
         <v>3772600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3934200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3990000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3857000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3682900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3839200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4022400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4324500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3775900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3800600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3927700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2218600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2277300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2216800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2086200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2584400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2821600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3213800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3096600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2845500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2341100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1853600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1526400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1620800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2000700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1768100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1913600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2144900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2133900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1826500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2318200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2777500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2847900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2827300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2826800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2344700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2256000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1831500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1855500</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2365800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2345600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1952600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1655900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1976900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2000300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1723700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1764200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1408300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1361700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1394900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1392100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>693900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>713100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>722800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>734800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>746800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>867700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>871700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>999800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1208600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1367300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1578900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1715000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1756600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1887600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1927100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2030600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2119100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1759100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1702900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1756300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1579600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1770000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1716300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1795400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>291400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>359500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>396700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>484700</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1600300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1592100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>781800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1482200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1462800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1401100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>698100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1720000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1744900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1952300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1234300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2073400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>689400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>652000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>783500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>821500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>755100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>811600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>777400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>812300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>848700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>952200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>980600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1174500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1396300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1473100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1525400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1465100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1551300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1538300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1533900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1542700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1477000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1582200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1726200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1069600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>914100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>928600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>928000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>919900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7812700</v>
+      </c>
+      <c r="E66" s="3">
         <v>7735900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7467300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7171100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7336900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7179000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6997000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7612200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7507700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7112900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7367200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7418700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3627200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3654000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5645600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5521700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6014200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6304700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6562900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6470200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6301000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5911900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5570100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5506900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5841300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6439000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6323900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6467800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6953000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6514900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6154600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6556300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6606200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7075900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7112100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6538200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4366800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4378700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>3931600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>4022200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,52 +7938,55 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13445100</v>
+      </c>
+      <c r="E72" s="3">
         <v>13356600</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3">
         <v>14778000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13315400</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14744700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14713100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14474000</v>
       </c>
-      <c r="M72" s="3" t="s">
+      <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15313200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14653700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15778800</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>8</v>
@@ -7826,8 +8000,8 @@
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -7880,17 +8054,20 @@
       <c r="AM72" s="3">
         <v>0</v>
       </c>
-      <c r="AN72" s="3" t="s">
+      <c r="AN72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>7221600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>7123800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12299600</v>
+      </c>
+      <c r="E76" s="3">
         <v>12197000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11944300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11975700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12004200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12108000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11968200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11940800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11881400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13029100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12418600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12436700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12386600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12229900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11846000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11900200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11776300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11415700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10535000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9704400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8549500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7841300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7286100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6686100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6548300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6499800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6611700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6536300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6630300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6586100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6393300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5939600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5257600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5339700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5010400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4888000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4728800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4683000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4391300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4310600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>343700</v>
+      </c>
+      <c r="E81" s="3">
         <v>213000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>122200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>215400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>67000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>280900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>31700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-727600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>361400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>413900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-739100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>626900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>374400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>39800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>152800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>799300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>775600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>998000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1202100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1022100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>602900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>600400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-48500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>44000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>70500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>95300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>180200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>218200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>350600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>523600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>293700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>338900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>180200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>194900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>249700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>261300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>118400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>228900</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>151500</v>
+      </c>
+      <c r="E83" s="3">
         <v>149800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>173000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>150600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>167200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>149700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>197600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>146600</v>
-      </c>
-      <c r="K83" s="3">
-        <v>134100</v>
       </c>
       <c r="L83" s="3">
         <v>134100</v>
       </c>
       <c r="M83" s="3">
+        <v>134100</v>
+      </c>
+      <c r="N83" s="3">
         <v>132800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>135900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>136900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>133700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>160400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>153200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>153400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>149500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>146200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>145200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>148800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>151600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>154000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>152400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>158300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>166400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>170800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>152400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>175000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>162900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>130100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>147500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>154400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>157300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>152400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>116300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>105000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>100600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>103900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>103100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>255800</v>
+      </c>
+      <c r="E89" s="3">
         <v>217300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>527500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>535400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1043600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>207000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>471500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>302700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>656500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>475500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>717700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1020000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>126900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>636400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1032200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1033700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>692300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1135100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>586000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>628400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>327800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>354900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>460000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>503700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>442800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>385800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>512200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>271100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>478500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>547700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>449300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>550100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>192100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>32100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>245300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>20700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>85800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>278100</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>220400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-431300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-405900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-462800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-710500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-809700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-517800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-561100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-446000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-409100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-449200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-596700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-429700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-230600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-203700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-158700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-136200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-160800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-124800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-121900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-110600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-161400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-129700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-120500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-71100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-110800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-257600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-307400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-259700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-275300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-209800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-175900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-114800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-131900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-97700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-126500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-100400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-98600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-83900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-100400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-104900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-141500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-502200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-487500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-729100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-494600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-273400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-243100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-606300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-78600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-447200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-438900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-42100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-889300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-602100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-267100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-413200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-42300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-621000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-307300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-136500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>19400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-313000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>10500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-709500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-164800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-306100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-448300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-239800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-202400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-147400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-86800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-113200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-109700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-101700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1714100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-101000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-113200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-69300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-123400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,56 +10455,57 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="3">
+        <v>255200</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>176700</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>353400</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>176700</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>431900</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>215900</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>353400</v>
       </c>
-      <c r="P96" s="3" t="s">
+      <c r="Q96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-176700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -10279,11 +10513,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-157000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300200</v>
+      </c>
+      <c r="E100" s="3">
         <v>346100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>185700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-330300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-523500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>167500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-63200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>183100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-555700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-52600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-234000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-371000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-163800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-236300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-631000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-135100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-188500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-84100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-552300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-29500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-162000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-224600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-239100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>119400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-188700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-193600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>288500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-56700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-537400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-184900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-418200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-181900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>24300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>1674800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-26400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>129500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-173800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-125400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>900</v>
+      </c>
+      <c r="E101" s="3">
         <v>38800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-88200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>15300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-83200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-41200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-14500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-27300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-13500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-16500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-21700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-14600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-21700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-15600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-22700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-15800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-22500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-13800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-9900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-186600</v>
+      </c>
+      <c r="E102" s="3">
         <v>86100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>208300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-534800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>26500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>139900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>77000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-105200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-61000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-65500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>895300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-299700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-433200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>179200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>755000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1071200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>513700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>329000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>178900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-66700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>297500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-142800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>226100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-451800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>386400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-117700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-139900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>313200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>213800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-148500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>169200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-105100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-46000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>205500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-107600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>102500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>34000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-29500</v>
       </c>
     </row>
